--- a/project3/data.xlsx
+++ b/project3/data.xlsx
@@ -20,18 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t xml:space="preserve">Count of MegaCityCapitals/Sec</t>
+    <t xml:space="preserve">Sum of MegaCityCapitals/Sec</t>
   </si>
   <si>
     <t xml:space="preserve">Column labels</t>
   </si>
   <si>
     <t xml:space="preserve">Row Labels</t>
-  </si>
-  <si>
-    <t>(blank)</t>
   </si>
   <si>
     <t xml:space="preserve">Grand Total</t>
@@ -131,6 +128,2020 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Performance vs Number of Capitals with NumT Variation</a:t>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smooth"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Sum of MegaCityCapitals/Sec</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Column labels</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Sum of MegaCityCapitals/Sec</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Column labels</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.653</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.695</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.308</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.602</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.416</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>54.598</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>54.779</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>67.683</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.858</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Sum of MegaCityCapitals/Sec</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Column labels</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.651</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.641</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.641</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20.48</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.93</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.355</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>58.285</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>75.039</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85.846</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Sum of MegaCityCapitals/Sec</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Column labels</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.139</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.99</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.38</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.781</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38.836</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42.177</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>63.921</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Sum of MegaCityCapitals/Sec</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Column labels</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.416</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.786</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.029</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.944</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.916</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.548</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40.252</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>54.866</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
+        <c:axId val="2140841463"/>
+        <c:axId val="2140841464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="50.000000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>Amount of Capitals</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>MegaCapitals/Sec</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="2673349" y="2505074"/>
+      <a:ext cx="5449743" cy="3260724"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Performance vs Number of Threads with # Capital Variation</a:t>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smooth"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>22.653</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.532</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.311</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>38.17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.651</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.416</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.359</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>43.695</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.641</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.139</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.786</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19.308</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.641</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.657</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>51.602</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.687</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$5:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>50.416</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.93</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.944</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.431</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$5:$H$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>54.598</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.355</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.781</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.916</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>54.779</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.285</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.836</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.548</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.907</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$5:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>67.683</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.039</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42.177</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40.252</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>39.454</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$5:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$5:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>69.858</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.846</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>63.921</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54.866</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44.268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
+        <c:axId val="2140841469"/>
+        <c:axId val="2140841470"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841469"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="8.000000"/>
+          <c:min val="1.000000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>Threads</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841470"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841470"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>MegaCapitals/Sec</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841469"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="8715373" y="2466973"/>
+      <a:ext cx="5577099" cy="3336924"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
               <a:defRPr sz="1400" b="0" spc="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
@@ -785,6 +2796,7 @@
         <c:dLbls>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
@@ -1130,7 +3142,489 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smooth"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Main!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Main!$A$2:$A$51</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Main!$B$2:$B$51</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Main!$C$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Main!$A$2:$A$51</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Main!$C$2:$C$51</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
+        <c:axId val="2140841475"/>
+        <c:axId val="2140841476"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841475"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841476"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841476"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841475"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="3644899" y="600075"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1715,7 +4209,1778 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>927099</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>598343</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1115853873" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="0">
+        <a:off x="2673349" y="2505074"/>
+        <a:ext cx="5449743" cy="3260724"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>295273</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>155574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>385972</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>114297</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="99749538" name="" descr="Curved Lines are in &#10;"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="0">
+        <a:off x="8715373" y="2466973"/>
+        <a:ext cx="5577099" cy="3336924"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>241299</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>53974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>488949</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1132287848" name=""/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="0" flipH="0" flipV="0">
+          <a:off x="13385799" y="5565774"/>
+          <a:ext cx="857250" cy="276224"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="overflow" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" upright="0" compatLnSpc="0"/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr/>
+            <a:t># Capitals</a:t>
+          </a:r>
+          <a:endParaRPr/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
@@ -1744,6 +6009,38 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>527049</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>203199</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="580219604" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="0">
+        <a:off x="3644899" y="600075"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2052,7 +6349,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:M11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A3:L10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
@@ -2061,7 +6358,7 @@
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
-        <item x="5"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2077,7 +6374,7 @@
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
-        <item x="10"/>
+        <item h="1" x="10"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2086,7 +6383,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
@@ -2102,9 +6399,6 @@
     <i>
       <x v="4"/>
     </i>
-    <i>
-      <x v="5"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2112,7 +6406,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="12">
+  <colItems count="11">
     <i>
       <x/>
     </i>
@@ -2143,15 +6437,12 @@
     <i>
       <x v="9"/>
     </i>
-    <i>
-      <x v="10"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of MegaCityCapitals/Sec" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of MegaCityCapitals/Sec" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
@@ -2555,14 +6846,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" min="1" max="1" width="27.6640625"/>
+    <col bestFit="1" min="1" max="1" width="26.140625"/>
     <col bestFit="1" min="2" max="2" width="15.47265625"/>
-    <col bestFit="1" min="3" max="5" width="1.76171875"/>
-    <col bestFit="1" min="6" max="11" width="2.8125"/>
-    <col bestFit="1" min="12" max="12" width="6.90234375"/>
-    <col bestFit="1" min="13" max="13" width="11.09375"/>
+    <col bestFit="1" min="3" max="6" width="6.5234375"/>
+    <col bestFit="1" min="7" max="11" width="7.57421875"/>
+    <col bestFit="1" min="12" max="13" width="11.09375"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2610,46 +6900,43 @@
       <c r="L4" t="s">
         <v>3</v>
       </c>
-      <c r="M4" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>22.652999999999999</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>38.170000000000002</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>43.695</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>19.308</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>51.601999999999997</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>50.415999999999997</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>54.597999999999999</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>54.779000000000003</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>67.683000000000007</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
+        <v>69.858000000000004</v>
+      </c>
+      <c r="L5">
+        <v>472.762</v>
       </c>
     </row>
     <row r="6">
@@ -2657,37 +6944,37 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>10.532</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>12.651</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>10.641</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>7.641</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>20.48</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>29.93</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>44.354999999999997</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>58.284999999999997</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>75.039000000000001</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
+        <v>85.846000000000004</v>
+      </c>
+      <c r="L6">
+        <v>355.39999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +6982,37 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4.6200000000000001</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>4.4299999999999997</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>7.1390000000000002</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>7.9900000000000002</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>9.9990000000000006</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>21.379999999999999</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>23.780999999999999</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>38.835999999999999</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>42.177</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+        <v>63.920999999999999</v>
+      </c>
+      <c r="L7">
+        <v>224.273</v>
       </c>
     </row>
     <row r="8">
@@ -2733,37 +7020,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3.532</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4.4160000000000004</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>5.7859999999999996</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>6.0289999999999999</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>7.5499999999999998</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>19.943999999999999</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>17.916</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>24.547999999999998</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>40.252000000000002</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>10</v>
+        <v>54.866</v>
+      </c>
+      <c r="L8">
+        <v>184.839</v>
       </c>
     </row>
     <row r="9">
@@ -2771,80 +7058,75 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3.3109999999999999</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4.359</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>5.3630000000000004</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>6.657</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>9.6869999999999994</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>13.430999999999999</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>17.911999999999999</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>28.907</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>39.454000000000001</v>
       </c>
       <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
+        <v>44.268000000000001</v>
+      </c>
+      <c r="L9">
+        <v>173.34899999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>5</v>
-      </c>
-      <c r="J11">
-        <v>5</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="M11">
-        <v>50</v>
+      <c r="B10">
+        <v>44.648000000000003</v>
+      </c>
+      <c r="C10">
+        <v>64.025999999999996</v>
+      </c>
+      <c r="D10">
+        <v>72.623999999999995</v>
+      </c>
+      <c r="E10">
+        <v>47.625</v>
+      </c>
+      <c r="F10">
+        <v>99.317999999999984</v>
+      </c>
+      <c r="G10">
+        <v>135.101</v>
+      </c>
+      <c r="H10">
+        <v>158.56200000000001</v>
+      </c>
+      <c r="I10">
+        <v>205.35499999999999</v>
+      </c>
+      <c r="J10">
+        <v>264.60500000000002</v>
+      </c>
+      <c r="K10">
+        <v>318.75900000000001</v>
+      </c>
+      <c r="L10">
+        <v>1410.6229999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2852,6 +7134,7 @@
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2865,13 +7148,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">
